--- a/outputs/evaluation/decision/v1/CF_M05/run_2/CF_M05_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_2/CF_M05_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,50 +504,50 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>This microservice has the main function of routing all communications to the corresponding microservice within the system architecture, acting as a central traffic management point.</t>
+          <t>AWS is a consolidated cloud platform with robust services and a reliable infrastructure. One of the great advantages of AWS is that it has a very wide selection of services: from the deployment of servers and databases, to AI, storage, security, and specific services for sectors. This diversity makes it easy to adapt to the needs of the project, allows growing and scaling the project in an agile way and eliminates the need to look for other platforms when requirements evolve. For this reason, AWS was chosen instead of other options like Google Cloud Platform or Microsoft Azure. Having so many services available leaves the effort to be concentrated on the development of the solution, without having to invest extra time in infrastructure issues. Another reason why AWS was chosen was that this platform invests heavily in security and certifications, manages multiple security levels and offers tools to protect data and infrastructure, facilitating compliance with legal regulations and international standards.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.7007</v>
+        <v>0.6086</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M05_C11</t>
+          <t>CF_M05_C01, *CF_M05_C12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Confidentiality</t>
+          <t>Appearance; Visual and Functional consistency</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Access Control Microservice</t>
+          <t>Portal Microservice</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -557,32 +557,32 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The Access Control microservice has as its main objective the management of user authentication and their permissions within the application.</t>
+          <t>AWS is a consolidated cloud platform with robust services and a reliable infrastructure. One of the great advantages of AWS is that it has a very wide selection of services: from the deployment of servers and databases, to AI, storage, security, and specific services for sectors. This diversity makes it easy to adapt to the needs of the project, allows growing and scaling the project in an agile way and eliminates the need to look for other platforms when requirements evolve. For this reason, AWS was chosen instead of other options like Google Cloud Platform or Microsoft Azure. Having so many services available leaves the effort to be concentrated on the development of the solution, without having to invest extra time in infrastructure issues. Another reason why AWS was chosen was that this platform invests heavily in security and certifications, manages multiple security levels and offers tools to protect data and infrastructure, facilitating compliance with legal regulations and international standards.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7119</v>
+        <v>0.6424</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>*CF_M05_C11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -590,266 +590,458 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Confidentiality</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Communication Log Microservice</t>
+          <t>Access Control Microservice</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>This microservice has the main function of routing all communications to the corresponding microservice within the system architecture, acting as a central traffic management point.</t>
+          <t>The application has an architecture based on microservices, consisting of dividing the system into a set of small, independent, and autonomous services.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.6888</v>
+        <v>0.6889</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>*CF_M05_C13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Presentation and user experience</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Communication Log Microservice</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated, clarifying roles, avoiding unnecessary coupling, and facilitating testing, reusing, and maintaining the code over time.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, that formulates service requests, and the server, that receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.6819</v>
+        <v>0.6181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD08</t>
+          <t>CF_M05_AD06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_P05</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Integrity; Security; Data persistence</t>
+          <t>Availability; Capacity; Access; Scalability</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Cloud Architecture</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated, clarifying roles, avoiding unnecessary coupling, and facilitating testing, reusing, and maintaining the code over time.</t>
+          <t>AWS is a consolidated cloud platform with robust services and a reliable infrastructure. One of the great advantages of AWS is that it has a very wide selection of services: from the deployment of servers and databases, to AI, storage, security, and specific services for sectors. This diversity makes it easy to adapt to the needs of the project, allows growing and scaling the project in an agile way and eliminates the need to look for other platforms when requirements evolve. For this reason, AWS was chosen instead of other options like Google Cloud Platform or Microsoft Azure. Having so many services available leaves the effort to be concentrated on the development of the solution, without having to invest extra time in infrastructure issues. Another reason why AWS was chosen was that this platform invests heavily in security and certifications, manages multiple security levels and offers tools to protect data and infrastructure, facilitating compliance with legal regulations and international standards.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.745</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>*CF_M05_C15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Capacity; Maintainability; Scalability</t>
+          <t>Presentation and user experience</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services, which allows building modern single-page applications (SPA) that render dynamic views and manage internal navigation without having to reload the page, improving fluidity of use.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, that formulates service requests, and the server, that receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.7437</v>
+        <v>0.7007</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>*CF_M05_C14</t>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>Integrity; Security; Data persistence</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Angular; Spring Boot</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated, clarifying roles, avoiding unnecessary coupling, and facilitating testing, reusing, and maintaining the code over time.</t>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated.</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.7173</v>
+        <v>0.7171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>CF_M05_AD09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>76</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Capacity; Maintainability; Scalability</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Angular</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6763</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AD10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>77</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Angular; Spring Boot</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>81</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Availability; Capacity</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>The application has an architecture based on microservices, consisting of dividing the system into a set of small, independent, and autonomous services.</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7136</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>78</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7287</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>CF_M05_AD13</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>*CF_M05_C18</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E13" t="n">
         <v>82</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Scalability</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Amazon EKS</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0.767</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AWS is a consolidated cloud platform with robust services and a reliable infrastructure. One of the great advantages of AWS is that it has a very wide selection of services: from the deployment of servers and databases, to AI, storage, security, and specific services for sectors. This diversity makes it easy to adapt to the needs of the project, allows growing and scaling the project in an agile way and eliminates the need to look for other platforms when requirements evolve. For this reason, AWS was chosen instead of other options like Google Cloud Platform or Microsoft Azure. Having so many services available leaves the effort to be concentrated on the development of the solution, without having to invest extra time in infrastructure issues. Another reason why AWS was chosen was that this platform invests heavily in security and certifications, manages multiple security levels and offers tools to protect data and infrastructure, facilitating compliance with legal regulations and international standards.</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7302</v>
       </c>
     </row>
   </sheetData>
